--- a/ВКР, отчет/ВКР, испытания.xlsx
+++ b/ВКР, отчет/ВКР, испытания.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Загрузки\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D44677CE-08D3-44A9-8C8B-2F7DF3A478E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97E50EF4-1788-4064-9B32-6B7240C257A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -563,7 +563,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -619,26 +619,29 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -667,27 +670,21 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -702,6 +699,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -995,58 +998,58 @@
   <sheetData>
     <row r="1" spans="2:20" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:20" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="44" t="s">
+      <c r="B2" s="43" t="s">
         <v>44</v>
       </c>
-      <c r="C2" s="30" t="s">
+      <c r="C2" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="31"/>
-      <c r="I2" s="31"/>
-      <c r="J2" s="32"/>
-      <c r="K2" s="37" t="s">
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="32"/>
+      <c r="J2" s="33"/>
+      <c r="K2" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="L2" s="38"/>
-      <c r="M2" s="38"/>
-      <c r="N2" s="38"/>
-      <c r="O2" s="38"/>
-      <c r="P2" s="38"/>
-      <c r="Q2" s="38"/>
-      <c r="R2" s="38"/>
-      <c r="S2" s="39"/>
+      <c r="L2" s="37"/>
+      <c r="M2" s="37"/>
+      <c r="N2" s="37"/>
+      <c r="O2" s="37"/>
+      <c r="P2" s="37"/>
+      <c r="Q2" s="37"/>
+      <c r="R2" s="37"/>
+      <c r="S2" s="38"/>
       <c r="T2" s="18" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="3" spans="2:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="45"/>
-      <c r="C3" s="42" t="s">
+      <c r="B3" s="44"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="D3" s="28" t="s">
+      <c r="E3" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="E3" s="28" t="s">
+      <c r="F3" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="28" t="s">
+      <c r="G3" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="H3" s="35" t="s">
+      <c r="H3" s="39" t="s">
         <v>38</v>
       </c>
-      <c r="I3" s="28" t="s">
+      <c r="I3" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="J3" s="33" t="s">
+      <c r="J3" s="34" t="s">
         <v>0</v>
       </c>
       <c r="K3" s="8" t="s">
@@ -1073,21 +1076,21 @@
       <c r="R3" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="S3" s="26" t="s">
+      <c r="S3" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="T3" s="25"/>
+      <c r="T3" s="19"/>
     </row>
     <row r="4" spans="2:20" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="46"/>
-      <c r="C4" s="43"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="29"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="29"/>
-      <c r="H4" s="36"/>
-      <c r="I4" s="29"/>
-      <c r="J4" s="34"/>
+      <c r="B4" s="45"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="42"/>
+      <c r="E4" s="30"/>
+      <c r="F4" s="30"/>
+      <c r="G4" s="30"/>
+      <c r="H4" s="40"/>
+      <c r="I4" s="30"/>
+      <c r="J4" s="35"/>
       <c r="K4" s="6" t="s">
         <v>8</v>
       </c>
@@ -1112,35 +1115,35 @@
       <c r="R4" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="S4" s="27"/>
-      <c r="T4" s="19"/>
+      <c r="S4" s="28"/>
+      <c r="T4" s="20"/>
     </row>
     <row r="5" spans="2:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="18">
         <v>1</v>
       </c>
-      <c r="C5" s="40" t="s">
+      <c r="C5" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="20" t="s">
+      <c r="E5" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="E5" s="20">
+      <c r="F5" s="22">
         <v>100</v>
       </c>
-      <c r="F5" s="20">
+      <c r="G5" s="22">
         <v>32</v>
       </c>
-      <c r="G5" s="20" t="s">
+      <c r="H5" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="H5" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="I5" s="20" t="s">
+      <c r="I5" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="J5" s="22" t="s">
+      <c r="J5" s="23" t="s">
         <v>27</v>
       </c>
       <c r="K5" s="14">
@@ -1174,15 +1177,15 @@
       <c r="T5" s="18"/>
     </row>
     <row r="6" spans="2:20" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="19"/>
-      <c r="C6" s="41"/>
-      <c r="D6" s="21"/>
+      <c r="B6" s="20"/>
+      <c r="C6" s="21"/>
+      <c r="D6" s="26"/>
       <c r="E6" s="21"/>
       <c r="F6" s="21"/>
       <c r="G6" s="21"/>
       <c r="H6" s="21"/>
       <c r="I6" s="21"/>
-      <c r="J6" s="23"/>
+      <c r="J6" s="24"/>
       <c r="K6" s="3">
         <v>0.64829999999999999</v>
       </c>
@@ -1211,34 +1214,34 @@
         <f>AVERAGE(K6:R6)</f>
         <v>0.72817499999999991</v>
       </c>
-      <c r="T6" s="19"/>
+      <c r="T6" s="20"/>
     </row>
     <row r="7" spans="2:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="18">
         <v>2</v>
       </c>
-      <c r="C7" s="40" t="s">
+      <c r="C7" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="D7" s="20" t="s">
+      <c r="E7" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="20">
+      <c r="F7" s="22">
         <v>100</v>
       </c>
-      <c r="F7" s="20">
+      <c r="G7" s="22">
         <v>32</v>
       </c>
-      <c r="G7" s="20" t="s">
+      <c r="H7" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="H7" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="I7" s="20" t="s">
+      <c r="I7" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="J7" s="22" t="s">
+      <c r="J7" s="23" t="s">
         <v>27</v>
       </c>
       <c r="K7" s="14">
@@ -1272,15 +1275,15 @@
       <c r="T7" s="18"/>
     </row>
     <row r="8" spans="2:20" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="19"/>
-      <c r="C8" s="41"/>
-      <c r="D8" s="21"/>
+      <c r="B8" s="20"/>
+      <c r="C8" s="21"/>
+      <c r="D8" s="26"/>
       <c r="E8" s="21"/>
       <c r="F8" s="21"/>
       <c r="G8" s="21"/>
       <c r="H8" s="21"/>
       <c r="I8" s="21"/>
-      <c r="J8" s="23"/>
+      <c r="J8" s="24"/>
       <c r="K8" s="3">
         <v>0.64690000000000003</v>
       </c>
@@ -1309,34 +1312,34 @@
         <f t="shared" si="0"/>
         <v>0.73016250000000005</v>
       </c>
-      <c r="T8" s="19"/>
+      <c r="T8" s="20"/>
     </row>
     <row r="9" spans="2:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="18">
         <v>3</v>
       </c>
-      <c r="C9" s="40" t="s">
+      <c r="C9" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="20" t="s">
+      <c r="E9" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="E9" s="20">
+      <c r="F9" s="22">
         <v>100</v>
       </c>
-      <c r="F9" s="20">
+      <c r="G9" s="22">
         <v>32</v>
       </c>
-      <c r="G9" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="H9" s="20" t="s">
+      <c r="H9" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="I9" s="20" t="s">
+      <c r="I9" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="J9" s="22" t="s">
+      <c r="J9" s="23" t="s">
         <v>27</v>
       </c>
       <c r="K9" s="14">
@@ -1370,17 +1373,17 @@
       <c r="T9" s="18"/>
     </row>
     <row r="10" spans="2:20" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="19"/>
-      <c r="C10" s="41"/>
-      <c r="D10" s="21"/>
+      <c r="B10" s="20"/>
+      <c r="C10" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" s="26"/>
       <c r="E10" s="21"/>
       <c r="F10" s="21"/>
-      <c r="G10" s="17" t="s">
-        <v>35</v>
-      </c>
+      <c r="G10" s="21"/>
       <c r="H10" s="21"/>
       <c r="I10" s="21"/>
-      <c r="J10" s="23"/>
+      <c r="J10" s="24"/>
       <c r="K10" s="3">
         <v>0.33710000000000001</v>
       </c>
@@ -1409,34 +1412,34 @@
         <f t="shared" si="0"/>
         <v>0.54801250000000001</v>
       </c>
-      <c r="T10" s="19"/>
+      <c r="T10" s="20"/>
     </row>
     <row r="11" spans="2:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="18">
         <v>4</v>
       </c>
-      <c r="C11" s="40" t="s">
+      <c r="C11" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="D11" s="20" t="s">
+      <c r="E11" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="E11" s="20">
+      <c r="F11" s="22">
         <v>100</v>
       </c>
-      <c r="F11" s="20">
+      <c r="G11" s="22">
         <v>32</v>
       </c>
-      <c r="G11" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="H11" s="20" t="s">
+      <c r="H11" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="I11" s="20" t="s">
+      <c r="I11" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="J11" s="22" t="s">
+      <c r="J11" s="23" t="s">
         <v>27</v>
       </c>
       <c r="K11" s="14">
@@ -1470,17 +1473,17 @@
       <c r="T11" s="18"/>
     </row>
     <row r="12" spans="2:20" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="19"/>
-      <c r="C12" s="41"/>
-      <c r="D12" s="21"/>
+      <c r="B12" s="20"/>
+      <c r="C12" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="D12" s="26"/>
       <c r="E12" s="21"/>
       <c r="F12" s="21"/>
-      <c r="G12" s="17" t="s">
-        <v>35</v>
-      </c>
+      <c r="G12" s="21"/>
       <c r="H12" s="21"/>
       <c r="I12" s="21"/>
-      <c r="J12" s="23"/>
+      <c r="J12" s="24"/>
       <c r="K12" s="3">
         <v>0.4279</v>
       </c>
@@ -1509,34 +1512,34 @@
         <f t="shared" si="1"/>
         <v>0.47669999999999996</v>
       </c>
-      <c r="T12" s="19"/>
+      <c r="T12" s="20"/>
     </row>
     <row r="13" spans="2:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="18">
         <v>5</v>
       </c>
-      <c r="C13" s="40" t="s">
+      <c r="C13" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="D13" s="20" t="s">
+      <c r="E13" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="E13" s="20">
+      <c r="F13" s="22">
         <v>100</v>
       </c>
-      <c r="F13" s="20">
+      <c r="G13" s="22">
         <v>32</v>
       </c>
-      <c r="G13" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="H13" s="20" t="s">
+      <c r="H13" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="I13" s="20" t="s">
+      <c r="I13" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="J13" s="22" t="s">
+      <c r="J13" s="23" t="s">
         <v>27</v>
       </c>
       <c r="K13" s="14">
@@ -1570,17 +1573,17 @@
       <c r="T13" s="18"/>
     </row>
     <row r="14" spans="2:20" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="19"/>
-      <c r="C14" s="41"/>
-      <c r="D14" s="21"/>
+      <c r="B14" s="20"/>
+      <c r="C14" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="D14" s="26"/>
       <c r="E14" s="21"/>
       <c r="F14" s="21"/>
-      <c r="G14" s="17" t="s">
-        <v>35</v>
-      </c>
+      <c r="G14" s="21"/>
       <c r="H14" s="21"/>
       <c r="I14" s="21"/>
-      <c r="J14" s="23"/>
+      <c r="J14" s="24"/>
       <c r="K14" s="3">
         <v>0.3921</v>
       </c>
@@ -1609,34 +1612,34 @@
         <f t="shared" si="1"/>
         <v>0.4924</v>
       </c>
-      <c r="T14" s="19"/>
+      <c r="T14" s="20"/>
     </row>
     <row r="15" spans="2:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="18">
         <v>6</v>
       </c>
-      <c r="C15" s="40" t="s">
+      <c r="C15" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="D15" s="20" t="s">
+      <c r="E15" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="E15" s="20">
+      <c r="F15" s="22">
         <v>100</v>
       </c>
-      <c r="F15" s="20">
+      <c r="G15" s="22">
         <v>32</v>
       </c>
-      <c r="G15" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="H15" s="20" t="s">
+      <c r="H15" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="I15" s="20" t="s">
+      <c r="I15" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="J15" s="22" t="s">
+      <c r="J15" s="23" t="s">
         <v>27</v>
       </c>
       <c r="K15" s="14">
@@ -1670,17 +1673,17 @@
       <c r="T15" s="18"/>
     </row>
     <row r="16" spans="2:20" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="19"/>
-      <c r="C16" s="41"/>
-      <c r="D16" s="21"/>
+      <c r="B16" s="20"/>
+      <c r="C16" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="D16" s="26"/>
       <c r="E16" s="21"/>
       <c r="F16" s="21"/>
-      <c r="G16" s="17" t="s">
-        <v>35</v>
-      </c>
+      <c r="G16" s="21"/>
       <c r="H16" s="21"/>
       <c r="I16" s="21"/>
-      <c r="J16" s="23"/>
+      <c r="J16" s="24"/>
       <c r="K16" s="3">
         <v>0.36780000000000002</v>
       </c>
@@ -1709,34 +1712,34 @@
         <f t="shared" si="1"/>
         <v>0.50178749999999994</v>
       </c>
-      <c r="T16" s="19"/>
+      <c r="T16" s="20"/>
     </row>
     <row r="17" spans="2:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="18">
         <v>7</v>
       </c>
-      <c r="C17" s="40" t="s">
+      <c r="C17" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="D17" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="D17" s="20" t="s">
+      <c r="E17" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="E17" s="20">
+      <c r="F17" s="22">
         <v>100</v>
       </c>
-      <c r="F17" s="20">
+      <c r="G17" s="22">
         <v>32</v>
       </c>
-      <c r="G17" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="H17" s="20" t="s">
+      <c r="H17" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="I17" s="20" t="s">
+      <c r="I17" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="J17" s="22" t="s">
+      <c r="J17" s="23" t="s">
         <v>27</v>
       </c>
       <c r="K17" s="14">
@@ -1772,17 +1775,17 @@
       </c>
     </row>
     <row r="18" spans="2:20" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="19"/>
-      <c r="C18" s="41"/>
-      <c r="D18" s="21"/>
+      <c r="B18" s="20"/>
+      <c r="C18" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="D18" s="26"/>
       <c r="E18" s="21"/>
       <c r="F18" s="21"/>
-      <c r="G18" s="17" t="s">
-        <v>35</v>
-      </c>
+      <c r="G18" s="21"/>
       <c r="H18" s="21"/>
       <c r="I18" s="21"/>
-      <c r="J18" s="23"/>
+      <c r="J18" s="24"/>
       <c r="K18" s="3">
         <v>0.40760000000000002</v>
       </c>
@@ -1811,34 +1814,34 @@
         <f t="shared" si="1"/>
         <v>0.47444999999999993</v>
       </c>
-      <c r="T18" s="19"/>
+      <c r="T18" s="20"/>
     </row>
     <row r="19" spans="2:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="18">
         <v>8</v>
       </c>
-      <c r="C19" s="40" t="s">
+      <c r="C19" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="D19" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="D19" s="20" t="s">
+      <c r="E19" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="E19" s="20">
+      <c r="F19" s="22">
         <v>100</v>
       </c>
-      <c r="F19" s="20">
+      <c r="G19" s="22">
         <v>32</v>
       </c>
-      <c r="G19" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="H19" s="20" t="s">
+      <c r="H19" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="I19" s="20" t="s">
+      <c r="I19" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="J19" s="22" t="s">
+      <c r="J19" s="23" t="s">
         <v>27</v>
       </c>
       <c r="K19" s="14">
@@ -1872,17 +1875,17 @@
       <c r="T19" s="18"/>
     </row>
     <row r="20" spans="2:20" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="19"/>
-      <c r="C20" s="41"/>
-      <c r="D20" s="21"/>
+      <c r="B20" s="20"/>
+      <c r="C20" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="D20" s="26"/>
       <c r="E20" s="21"/>
       <c r="F20" s="21"/>
-      <c r="G20" s="17" t="s">
-        <v>42</v>
-      </c>
+      <c r="G20" s="21"/>
       <c r="H20" s="21"/>
       <c r="I20" s="21"/>
-      <c r="J20" s="23"/>
+      <c r="J20" s="24"/>
       <c r="K20" s="3">
         <v>0.39069999999999999</v>
       </c>
@@ -1911,34 +1914,34 @@
         <f t="shared" si="1"/>
         <v>0.48515000000000003</v>
       </c>
-      <c r="T20" s="19"/>
+      <c r="T20" s="20"/>
     </row>
     <row r="21" spans="2:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="18">
         <v>9</v>
       </c>
-      <c r="C21" s="40" t="s">
+      <c r="C21" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="D21" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="D21" s="20" t="s">
+      <c r="E21" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="E21" s="20">
+      <c r="F21" s="22">
         <v>100</v>
       </c>
-      <c r="F21" s="20">
+      <c r="G21" s="22">
         <v>32</v>
       </c>
-      <c r="G21" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="H21" s="20" t="s">
+      <c r="H21" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="I21" s="20" t="s">
+      <c r="I21" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="J21" s="22" t="s">
+      <c r="J21" s="23" t="s">
         <v>27</v>
       </c>
       <c r="K21" s="14">
@@ -1972,17 +1975,17 @@
       <c r="T21" s="18"/>
     </row>
     <row r="22" spans="2:20" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="19"/>
-      <c r="C22" s="41"/>
-      <c r="D22" s="21"/>
+      <c r="B22" s="20"/>
+      <c r="C22" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="D22" s="26"/>
       <c r="E22" s="21"/>
       <c r="F22" s="21"/>
-      <c r="G22" s="17" t="s">
-        <v>43</v>
-      </c>
+      <c r="G22" s="21"/>
       <c r="H22" s="21"/>
       <c r="I22" s="21"/>
-      <c r="J22" s="23"/>
+      <c r="J22" s="24"/>
       <c r="K22" s="3">
         <v>0.29199999999999998</v>
       </c>
@@ -2011,20 +2014,20 @@
         <f t="shared" si="1"/>
         <v>0.52127499999999993</v>
       </c>
-      <c r="T22" s="19"/>
+      <c r="T22" s="20"/>
     </row>
     <row r="23" spans="2:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="18">
         <v>10</v>
       </c>
-      <c r="C23" s="40"/>
-      <c r="D23" s="20"/>
-      <c r="E23" s="20"/>
-      <c r="F23" s="20"/>
-      <c r="G23" s="24"/>
-      <c r="H23" s="20"/>
-      <c r="I23" s="20"/>
-      <c r="J23" s="22"/>
+      <c r="C23" s="46"/>
+      <c r="D23" s="25"/>
+      <c r="E23" s="22"/>
+      <c r="F23" s="22"/>
+      <c r="G23" s="22"/>
+      <c r="H23" s="22"/>
+      <c r="I23" s="22"/>
+      <c r="J23" s="23"/>
       <c r="K23" s="14"/>
       <c r="L23" s="2"/>
       <c r="M23" s="2"/>
@@ -2040,15 +2043,15 @@
       <c r="T23" s="18"/>
     </row>
     <row r="24" spans="2:20" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="19"/>
-      <c r="C24" s="41"/>
-      <c r="D24" s="21"/>
+      <c r="B24" s="20"/>
+      <c r="C24" s="47"/>
+      <c r="D24" s="26"/>
       <c r="E24" s="21"/>
       <c r="F24" s="21"/>
       <c r="G24" s="21"/>
       <c r="H24" s="21"/>
       <c r="I24" s="21"/>
-      <c r="J24" s="23"/>
+      <c r="J24" s="24"/>
       <c r="K24" s="3"/>
       <c r="L24" s="4"/>
       <c r="M24" s="4"/>
@@ -2061,20 +2064,20 @@
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T24" s="19"/>
+      <c r="T24" s="20"/>
     </row>
     <row r="25" spans="2:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="18">
         <v>11</v>
       </c>
-      <c r="C25" s="40"/>
-      <c r="D25" s="20"/>
-      <c r="E25" s="20"/>
-      <c r="F25" s="20"/>
-      <c r="G25" s="24"/>
-      <c r="H25" s="20"/>
-      <c r="I25" s="20"/>
-      <c r="J25" s="22"/>
+      <c r="C25" s="46"/>
+      <c r="D25" s="25"/>
+      <c r="E25" s="22"/>
+      <c r="F25" s="22"/>
+      <c r="G25" s="22"/>
+      <c r="H25" s="22"/>
+      <c r="I25" s="22"/>
+      <c r="J25" s="23"/>
       <c r="K25" s="14"/>
       <c r="L25" s="2"/>
       <c r="M25" s="2"/>
@@ -2090,15 +2093,15 @@
       <c r="T25" s="18"/>
     </row>
     <row r="26" spans="2:20" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="19"/>
-      <c r="C26" s="41"/>
-      <c r="D26" s="21"/>
+      <c r="B26" s="20"/>
+      <c r="C26" s="47"/>
+      <c r="D26" s="26"/>
       <c r="E26" s="21"/>
       <c r="F26" s="21"/>
       <c r="G26" s="21"/>
       <c r="H26" s="21"/>
       <c r="I26" s="21"/>
-      <c r="J26" s="23"/>
+      <c r="J26" s="24"/>
       <c r="K26" s="3"/>
       <c r="L26" s="4"/>
       <c r="M26" s="4"/>
@@ -2111,20 +2114,20 @@
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T26" s="19"/>
+      <c r="T26" s="20"/>
     </row>
     <row r="27" spans="2:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="18">
         <v>12</v>
       </c>
-      <c r="C27" s="40"/>
-      <c r="D27" s="20"/>
-      <c r="E27" s="20"/>
-      <c r="F27" s="20"/>
-      <c r="G27" s="24"/>
-      <c r="H27" s="20"/>
-      <c r="I27" s="20"/>
-      <c r="J27" s="22"/>
+      <c r="C27" s="46"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="22"/>
+      <c r="F27" s="22"/>
+      <c r="G27" s="22"/>
+      <c r="H27" s="22"/>
+      <c r="I27" s="22"/>
+      <c r="J27" s="23"/>
       <c r="K27" s="14"/>
       <c r="L27" s="2"/>
       <c r="M27" s="2"/>
@@ -2140,15 +2143,15 @@
       <c r="T27" s="18"/>
     </row>
     <row r="28" spans="2:20" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="19"/>
-      <c r="C28" s="41"/>
-      <c r="D28" s="21"/>
+      <c r="B28" s="20"/>
+      <c r="C28" s="47"/>
+      <c r="D28" s="26"/>
       <c r="E28" s="21"/>
       <c r="F28" s="21"/>
       <c r="G28" s="21"/>
       <c r="H28" s="21"/>
       <c r="I28" s="21"/>
-      <c r="J28" s="23"/>
+      <c r="J28" s="24"/>
       <c r="K28" s="3"/>
       <c r="L28" s="4"/>
       <c r="M28" s="4"/>
@@ -2161,20 +2164,20 @@
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T28" s="19"/>
+      <c r="T28" s="20"/>
     </row>
     <row r="29" spans="2:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="18">
         <v>13</v>
       </c>
-      <c r="C29" s="40"/>
-      <c r="D29" s="20"/>
-      <c r="E29" s="20"/>
-      <c r="F29" s="20"/>
-      <c r="G29" s="24"/>
-      <c r="H29" s="20"/>
-      <c r="I29" s="20"/>
-      <c r="J29" s="22"/>
+      <c r="C29" s="46"/>
+      <c r="D29" s="25"/>
+      <c r="E29" s="22"/>
+      <c r="F29" s="22"/>
+      <c r="G29" s="22"/>
+      <c r="H29" s="22"/>
+      <c r="I29" s="22"/>
+      <c r="J29" s="23"/>
       <c r="K29" s="14"/>
       <c r="L29" s="2"/>
       <c r="M29" s="2"/>
@@ -2190,15 +2193,15 @@
       <c r="T29" s="18"/>
     </row>
     <row r="30" spans="2:20" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="19"/>
-      <c r="C30" s="41"/>
-      <c r="D30" s="21"/>
+      <c r="B30" s="20"/>
+      <c r="C30" s="47"/>
+      <c r="D30" s="26"/>
       <c r="E30" s="21"/>
       <c r="F30" s="21"/>
       <c r="G30" s="21"/>
       <c r="H30" s="21"/>
       <c r="I30" s="21"/>
-      <c r="J30" s="23"/>
+      <c r="J30" s="24"/>
       <c r="K30" s="3"/>
       <c r="L30" s="4"/>
       <c r="M30" s="4"/>
@@ -2211,20 +2214,20 @@
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T30" s="19"/>
+      <c r="T30" s="20"/>
     </row>
     <row r="31" spans="2:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="18">
         <v>14</v>
       </c>
-      <c r="C31" s="40"/>
-      <c r="D31" s="20"/>
-      <c r="E31" s="20"/>
-      <c r="F31" s="20"/>
-      <c r="G31" s="24"/>
-      <c r="H31" s="20"/>
-      <c r="I31" s="20"/>
-      <c r="J31" s="22"/>
+      <c r="C31" s="46"/>
+      <c r="D31" s="25"/>
+      <c r="E31" s="22"/>
+      <c r="F31" s="22"/>
+      <c r="G31" s="22"/>
+      <c r="H31" s="22"/>
+      <c r="I31" s="22"/>
+      <c r="J31" s="23"/>
       <c r="K31" s="14"/>
       <c r="L31" s="2"/>
       <c r="M31" s="2"/>
@@ -2240,15 +2243,15 @@
       <c r="T31" s="18"/>
     </row>
     <row r="32" spans="2:20" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="19"/>
-      <c r="C32" s="41"/>
-      <c r="D32" s="21"/>
+      <c r="B32" s="20"/>
+      <c r="C32" s="47"/>
+      <c r="D32" s="26"/>
       <c r="E32" s="21"/>
       <c r="F32" s="21"/>
       <c r="G32" s="21"/>
       <c r="H32" s="21"/>
       <c r="I32" s="21"/>
-      <c r="J32" s="23"/>
+      <c r="J32" s="24"/>
       <c r="K32" s="3"/>
       <c r="L32" s="4"/>
       <c r="M32" s="4"/>
@@ -2261,20 +2264,20 @@
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T32" s="19"/>
+      <c r="T32" s="20"/>
     </row>
     <row r="33" spans="2:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="18">
         <v>15</v>
       </c>
-      <c r="C33" s="40"/>
-      <c r="D33" s="20"/>
-      <c r="E33" s="20"/>
-      <c r="F33" s="20"/>
-      <c r="G33" s="24"/>
-      <c r="H33" s="20"/>
-      <c r="I33" s="20"/>
-      <c r="J33" s="22"/>
+      <c r="C33" s="46"/>
+      <c r="D33" s="25"/>
+      <c r="E33" s="22"/>
+      <c r="F33" s="22"/>
+      <c r="G33" s="22"/>
+      <c r="H33" s="22"/>
+      <c r="I33" s="22"/>
+      <c r="J33" s="23"/>
       <c r="K33" s="14"/>
       <c r="L33" s="2"/>
       <c r="M33" s="2"/>
@@ -2290,15 +2293,15 @@
       <c r="T33" s="18"/>
     </row>
     <row r="34" spans="2:20" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="19"/>
-      <c r="C34" s="41"/>
-      <c r="D34" s="21"/>
+      <c r="B34" s="20"/>
+      <c r="C34" s="47"/>
+      <c r="D34" s="26"/>
       <c r="E34" s="21"/>
       <c r="F34" s="21"/>
       <c r="G34" s="21"/>
       <c r="H34" s="21"/>
       <c r="I34" s="21"/>
-      <c r="J34" s="23"/>
+      <c r="J34" s="24"/>
       <c r="K34" s="3"/>
       <c r="L34" s="4"/>
       <c r="M34" s="4"/>
@@ -2311,20 +2314,20 @@
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T34" s="19"/>
+      <c r="T34" s="20"/>
     </row>
     <row r="35" spans="2:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="18">
         <v>16</v>
       </c>
-      <c r="C35" s="40"/>
-      <c r="D35" s="20"/>
-      <c r="E35" s="20"/>
-      <c r="F35" s="20"/>
-      <c r="G35" s="24"/>
-      <c r="H35" s="20"/>
-      <c r="I35" s="20"/>
-      <c r="J35" s="22"/>
+      <c r="C35" s="46"/>
+      <c r="D35" s="25"/>
+      <c r="E35" s="22"/>
+      <c r="F35" s="22"/>
+      <c r="G35" s="22"/>
+      <c r="H35" s="22"/>
+      <c r="I35" s="22"/>
+      <c r="J35" s="23"/>
       <c r="K35" s="14"/>
       <c r="L35" s="2"/>
       <c r="M35" s="2"/>
@@ -2340,15 +2343,15 @@
       <c r="T35" s="18"/>
     </row>
     <row r="36" spans="2:20" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="19"/>
-      <c r="C36" s="41"/>
-      <c r="D36" s="21"/>
+      <c r="B36" s="20"/>
+      <c r="C36" s="47"/>
+      <c r="D36" s="26"/>
       <c r="E36" s="21"/>
       <c r="F36" s="21"/>
       <c r="G36" s="21"/>
       <c r="H36" s="21"/>
       <c r="I36" s="21"/>
-      <c r="J36" s="23"/>
+      <c r="J36" s="24"/>
       <c r="K36" s="3"/>
       <c r="L36" s="4"/>
       <c r="M36" s="4"/>
@@ -2361,20 +2364,20 @@
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T36" s="19"/>
+      <c r="T36" s="20"/>
     </row>
     <row r="37" spans="2:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="18">
         <v>17</v>
       </c>
-      <c r="C37" s="40"/>
-      <c r="D37" s="20"/>
-      <c r="E37" s="20"/>
-      <c r="F37" s="20"/>
-      <c r="G37" s="24"/>
-      <c r="H37" s="20"/>
-      <c r="I37" s="20"/>
-      <c r="J37" s="22"/>
+      <c r="C37" s="46"/>
+      <c r="D37" s="25"/>
+      <c r="E37" s="22"/>
+      <c r="F37" s="22"/>
+      <c r="G37" s="22"/>
+      <c r="H37" s="22"/>
+      <c r="I37" s="22"/>
+      <c r="J37" s="23"/>
       <c r="K37" s="14"/>
       <c r="L37" s="2"/>
       <c r="M37" s="2"/>
@@ -2390,15 +2393,15 @@
       <c r="T37" s="18"/>
     </row>
     <row r="38" spans="2:20" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B38" s="19"/>
-      <c r="C38" s="41"/>
-      <c r="D38" s="21"/>
+      <c r="B38" s="20"/>
+      <c r="C38" s="47"/>
+      <c r="D38" s="26"/>
       <c r="E38" s="21"/>
       <c r="F38" s="21"/>
       <c r="G38" s="21"/>
       <c r="H38" s="21"/>
       <c r="I38" s="21"/>
-      <c r="J38" s="23"/>
+      <c r="J38" s="24"/>
       <c r="K38" s="3"/>
       <c r="L38" s="4"/>
       <c r="M38" s="4"/>
@@ -2411,20 +2414,20 @@
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T38" s="19"/>
+      <c r="T38" s="20"/>
     </row>
     <row r="39" spans="2:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="18">
         <v>18</v>
       </c>
-      <c r="C39" s="40"/>
-      <c r="D39" s="20"/>
-      <c r="E39" s="20"/>
-      <c r="F39" s="20"/>
-      <c r="G39" s="24"/>
-      <c r="H39" s="20"/>
-      <c r="I39" s="20"/>
-      <c r="J39" s="22"/>
+      <c r="C39" s="46"/>
+      <c r="D39" s="25"/>
+      <c r="E39" s="22"/>
+      <c r="F39" s="22"/>
+      <c r="G39" s="22"/>
+      <c r="H39" s="22"/>
+      <c r="I39" s="22"/>
+      <c r="J39" s="23"/>
       <c r="K39" s="14"/>
       <c r="L39" s="2"/>
       <c r="M39" s="2"/>
@@ -2440,15 +2443,15 @@
       <c r="T39" s="18"/>
     </row>
     <row r="40" spans="2:20" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B40" s="19"/>
-      <c r="C40" s="41"/>
-      <c r="D40" s="21"/>
+      <c r="B40" s="20"/>
+      <c r="C40" s="47"/>
+      <c r="D40" s="26"/>
       <c r="E40" s="21"/>
       <c r="F40" s="21"/>
       <c r="G40" s="21"/>
       <c r="H40" s="21"/>
       <c r="I40" s="21"/>
-      <c r="J40" s="23"/>
+      <c r="J40" s="24"/>
       <c r="K40" s="3"/>
       <c r="L40" s="4"/>
       <c r="M40" s="4"/>
@@ -2461,20 +2464,20 @@
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T40" s="19"/>
+      <c r="T40" s="20"/>
     </row>
     <row r="41" spans="2:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="18">
         <v>19</v>
       </c>
-      <c r="C41" s="40"/>
-      <c r="D41" s="20"/>
-      <c r="E41" s="20"/>
-      <c r="F41" s="20"/>
-      <c r="G41" s="24"/>
-      <c r="H41" s="20"/>
-      <c r="I41" s="20"/>
-      <c r="J41" s="22"/>
+      <c r="C41" s="46"/>
+      <c r="D41" s="25"/>
+      <c r="E41" s="22"/>
+      <c r="F41" s="22"/>
+      <c r="G41" s="22"/>
+      <c r="H41" s="22"/>
+      <c r="I41" s="22"/>
+      <c r="J41" s="23"/>
       <c r="K41" s="14"/>
       <c r="L41" s="2"/>
       <c r="M41" s="2"/>
@@ -2490,15 +2493,15 @@
       <c r="T41" s="18"/>
     </row>
     <row r="42" spans="2:20" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B42" s="19"/>
-      <c r="C42" s="41"/>
-      <c r="D42" s="21"/>
+      <c r="B42" s="20"/>
+      <c r="C42" s="47"/>
+      <c r="D42" s="26"/>
       <c r="E42" s="21"/>
       <c r="F42" s="21"/>
       <c r="G42" s="21"/>
       <c r="H42" s="21"/>
       <c r="I42" s="21"/>
-      <c r="J42" s="23"/>
+      <c r="J42" s="24"/>
       <c r="K42" s="3"/>
       <c r="L42" s="4"/>
       <c r="M42" s="4"/>
@@ -2511,20 +2514,20 @@
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T42" s="19"/>
+      <c r="T42" s="20"/>
     </row>
     <row r="43" spans="2:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="18">
         <v>20</v>
       </c>
-      <c r="C43" s="40"/>
-      <c r="D43" s="20"/>
-      <c r="E43" s="20"/>
-      <c r="F43" s="20"/>
-      <c r="G43" s="24"/>
-      <c r="H43" s="20"/>
-      <c r="I43" s="20"/>
-      <c r="J43" s="22"/>
+      <c r="C43" s="46"/>
+      <c r="D43" s="25"/>
+      <c r="E43" s="22"/>
+      <c r="F43" s="22"/>
+      <c r="G43" s="22"/>
+      <c r="H43" s="22"/>
+      <c r="I43" s="22"/>
+      <c r="J43" s="23"/>
       <c r="K43" s="14"/>
       <c r="L43" s="2"/>
       <c r="M43" s="2"/>
@@ -2540,15 +2543,15 @@
       <c r="T43" s="18"/>
     </row>
     <row r="44" spans="2:20" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B44" s="19"/>
-      <c r="C44" s="41"/>
-      <c r="D44" s="21"/>
+      <c r="B44" s="20"/>
+      <c r="C44" s="47"/>
+      <c r="D44" s="26"/>
       <c r="E44" s="21"/>
       <c r="F44" s="21"/>
       <c r="G44" s="21"/>
       <c r="H44" s="21"/>
       <c r="I44" s="21"/>
-      <c r="J44" s="23"/>
+      <c r="J44" s="24"/>
       <c r="K44" s="3"/>
       <c r="L44" s="4"/>
       <c r="M44" s="4"/>
@@ -2561,53 +2564,48 @@
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T44" s="19"/>
+      <c r="T44" s="20"/>
     </row>
   </sheetData>
-  <mergeCells count="206">
-    <mergeCell ref="G43:G44"/>
+  <mergeCells count="195">
     <mergeCell ref="H43:H44"/>
     <mergeCell ref="I43:I44"/>
     <mergeCell ref="J43:J44"/>
     <mergeCell ref="T43:T44"/>
     <mergeCell ref="B43:B44"/>
-    <mergeCell ref="C43:C44"/>
     <mergeCell ref="D43:D44"/>
     <mergeCell ref="E43:E44"/>
     <mergeCell ref="F43:F44"/>
-    <mergeCell ref="G41:G42"/>
+    <mergeCell ref="G43:G44"/>
     <mergeCell ref="H41:H42"/>
     <mergeCell ref="I41:I42"/>
     <mergeCell ref="J41:J42"/>
     <mergeCell ref="T41:T42"/>
     <mergeCell ref="B41:B42"/>
-    <mergeCell ref="C41:C42"/>
     <mergeCell ref="D41:D42"/>
     <mergeCell ref="E41:E42"/>
     <mergeCell ref="F41:F42"/>
-    <mergeCell ref="G39:G40"/>
+    <mergeCell ref="G41:G42"/>
     <mergeCell ref="H39:H40"/>
     <mergeCell ref="I39:I40"/>
     <mergeCell ref="J39:J40"/>
     <mergeCell ref="T39:T40"/>
     <mergeCell ref="B39:B40"/>
-    <mergeCell ref="C39:C40"/>
     <mergeCell ref="D39:D40"/>
     <mergeCell ref="E39:E40"/>
     <mergeCell ref="F39:F40"/>
-    <mergeCell ref="G37:G38"/>
+    <mergeCell ref="G39:G40"/>
     <mergeCell ref="H37:H38"/>
     <mergeCell ref="I37:I38"/>
     <mergeCell ref="J37:J38"/>
     <mergeCell ref="T37:T38"/>
     <mergeCell ref="B37:B38"/>
-    <mergeCell ref="C37:C38"/>
     <mergeCell ref="D37:D38"/>
     <mergeCell ref="E37:E38"/>
     <mergeCell ref="F37:F38"/>
+    <mergeCell ref="G37:G38"/>
     <mergeCell ref="T33:T34"/>
     <mergeCell ref="B35:B36"/>
-    <mergeCell ref="C35:C36"/>
     <mergeCell ref="D35:D36"/>
     <mergeCell ref="E35:E36"/>
     <mergeCell ref="F35:F36"/>
@@ -2616,18 +2614,17 @@
     <mergeCell ref="I35:I36"/>
     <mergeCell ref="J35:J36"/>
     <mergeCell ref="T35:T36"/>
-    <mergeCell ref="F33:F34"/>
     <mergeCell ref="G33:G34"/>
     <mergeCell ref="H33:H34"/>
     <mergeCell ref="I33:I34"/>
     <mergeCell ref="J33:J34"/>
     <mergeCell ref="B29:B30"/>
     <mergeCell ref="B33:B34"/>
-    <mergeCell ref="C33:C34"/>
     <mergeCell ref="D33:D34"/>
     <mergeCell ref="E33:E34"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="C31:C32"/>
+    <mergeCell ref="F33:F34"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="D31:D32"/>
     <mergeCell ref="B2:B4"/>
     <mergeCell ref="B31:B32"/>
     <mergeCell ref="B5:B6"/>
@@ -2642,16 +2639,15 @@
     <mergeCell ref="B23:B24"/>
     <mergeCell ref="B25:B26"/>
     <mergeCell ref="B27:B28"/>
-    <mergeCell ref="C21:C22"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="D3:D4"/>
     <mergeCell ref="H29:H30"/>
     <mergeCell ref="I29:I30"/>
     <mergeCell ref="J29:J30"/>
     <mergeCell ref="T29:T30"/>
-    <mergeCell ref="D31:D32"/>
     <mergeCell ref="E31:E32"/>
     <mergeCell ref="F31:F32"/>
     <mergeCell ref="G31:G32"/>
@@ -2659,7 +2655,6 @@
     <mergeCell ref="I31:I32"/>
     <mergeCell ref="J31:J32"/>
     <mergeCell ref="T31:T32"/>
-    <mergeCell ref="C29:C30"/>
     <mergeCell ref="D29:D30"/>
     <mergeCell ref="E29:E30"/>
     <mergeCell ref="F29:F30"/>
@@ -2668,7 +2663,6 @@
     <mergeCell ref="I25:I26"/>
     <mergeCell ref="J25:J26"/>
     <mergeCell ref="T25:T26"/>
-    <mergeCell ref="D27:D28"/>
     <mergeCell ref="E27:E28"/>
     <mergeCell ref="F27:F28"/>
     <mergeCell ref="G27:G28"/>
@@ -2676,92 +2670,74 @@
     <mergeCell ref="I27:I28"/>
     <mergeCell ref="J27:J28"/>
     <mergeCell ref="T27:T28"/>
-    <mergeCell ref="C25:C26"/>
     <mergeCell ref="D25:D26"/>
     <mergeCell ref="E25:E26"/>
     <mergeCell ref="F25:F26"/>
     <mergeCell ref="G25:G26"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="H9:H10"/>
     <mergeCell ref="K2:S2"/>
     <mergeCell ref="H3:H4"/>
-    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="F3:F4"/>
     <mergeCell ref="E3:E4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="C5:C6"/>
     <mergeCell ref="D5:D6"/>
     <mergeCell ref="E5:E6"/>
-    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="F5:F6"/>
     <mergeCell ref="H5:H6"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="H7:H8"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="E9:E10"/>
-    <mergeCell ref="H9:H10"/>
     <mergeCell ref="I9:I10"/>
-    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="G9:G10"/>
     <mergeCell ref="T2:T4"/>
     <mergeCell ref="T5:T6"/>
     <mergeCell ref="T7:T8"/>
     <mergeCell ref="T9:T10"/>
     <mergeCell ref="S3:S4"/>
     <mergeCell ref="J9:J10"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="G5:G6"/>
     <mergeCell ref="J5:J6"/>
     <mergeCell ref="I7:I8"/>
     <mergeCell ref="J7:J8"/>
     <mergeCell ref="I5:I6"/>
-    <mergeCell ref="C2:J2"/>
+    <mergeCell ref="D2:J2"/>
     <mergeCell ref="J3:J4"/>
     <mergeCell ref="I3:I4"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="E9:E10"/>
     <mergeCell ref="H11:H12"/>
     <mergeCell ref="I11:I12"/>
     <mergeCell ref="J11:J12"/>
-    <mergeCell ref="D13:D14"/>
     <mergeCell ref="E13:E14"/>
     <mergeCell ref="F13:F14"/>
+    <mergeCell ref="G13:G14"/>
     <mergeCell ref="H13:H14"/>
     <mergeCell ref="I13:I14"/>
-    <mergeCell ref="D11:D12"/>
     <mergeCell ref="E11:E12"/>
     <mergeCell ref="F11:F12"/>
-    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="J13:J14"/>
     <mergeCell ref="D15:D16"/>
     <mergeCell ref="E15:E16"/>
     <mergeCell ref="F15:F16"/>
+    <mergeCell ref="G15:G16"/>
     <mergeCell ref="H15:H16"/>
     <mergeCell ref="H19:H20"/>
     <mergeCell ref="I19:I20"/>
     <mergeCell ref="J19:J20"/>
-    <mergeCell ref="D17:D18"/>
     <mergeCell ref="E17:E18"/>
     <mergeCell ref="F17:F18"/>
+    <mergeCell ref="G17:G18"/>
     <mergeCell ref="H17:H18"/>
-    <mergeCell ref="C19:C20"/>
     <mergeCell ref="D19:D20"/>
     <mergeCell ref="E19:E20"/>
     <mergeCell ref="F19:F20"/>
-    <mergeCell ref="H23:H24"/>
-    <mergeCell ref="I23:I24"/>
-    <mergeCell ref="J23:J24"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="E21:E22"/>
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="H21:H22"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="D23:D24"/>
-    <mergeCell ref="E23:E24"/>
-    <mergeCell ref="F23:F24"/>
-    <mergeCell ref="G23:G24"/>
-    <mergeCell ref="I21:I22"/>
-    <mergeCell ref="J21:J22"/>
+    <mergeCell ref="G19:G20"/>
     <mergeCell ref="I17:I18"/>
     <mergeCell ref="J17:J18"/>
-    <mergeCell ref="J13:J14"/>
     <mergeCell ref="I15:I16"/>
     <mergeCell ref="J15:J16"/>
     <mergeCell ref="T23:T24"/>
@@ -2771,6 +2747,22 @@
     <mergeCell ref="T17:T18"/>
     <mergeCell ref="T19:T20"/>
     <mergeCell ref="T21:T22"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="H23:H24"/>
+    <mergeCell ref="I23:I24"/>
+    <mergeCell ref="J23:J24"/>
+    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="H21:H22"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="E23:E24"/>
+    <mergeCell ref="F23:F24"/>
+    <mergeCell ref="G23:G24"/>
+    <mergeCell ref="I21:I22"/>
+    <mergeCell ref="J21:J22"/>
+    <mergeCell ref="C2:C4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
